--- a/PY_pytest/DataDriven_Excel/Excel/Book1.xlsx
+++ b/PY_pytest/DataDriven_Excel/Excel/Book1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04536FFD-87EF-4DC1-BA13-B9CC3B827A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C0EC52BB-5392-49AF-A519-25F7A9E8E93D}"/>
+    <workbookView xWindow="2340" yWindow="2385" windowWidth="21600" windowHeight="11295" xr2:uid="{C0EC52BB-5392-49AF-A519-25F7A9E8E93D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
